--- a/Libraries/Vehicle/Suspension/DOF15/sm_car_data_Susp_DOF15.xlsx
+++ b/Libraries/Vehicle/Suspension/DOF15/sm_car_data_Susp_DOF15.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vtpVDG\Libraries\Vehicle\Suspension\DOF15\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\DOF15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB74CB8-35B3-464F-8C51-D4BD01208306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3289CD00-7522-4AFE-BF5C-82E98E66479A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30405" yWindow="2610" windowWidth="21600" windowHeight="11235" tabRatio="964" activeTab="5" xr2:uid="{CCC96D31-0125-4D00-84F2-6850554951C3}"/>
+    <workbookView xWindow="33060" yWindow="2265" windowWidth="21600" windowHeight="11295" tabRatio="964" activeTab="3" xr2:uid="{CCC96D31-0125-4D00-84F2-6850554951C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="1" r:id="rId1"/>
@@ -5144,7 +5144,7 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9">
-        <v>50000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -5725,7 +5725,8 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9">
-        <v>-0.15</v>
+        <f>-0.15-0.1</f>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
